--- a/data/Mörel-Filet/investment_decision/Mörel_SFH_until_2004_investment_decision.xlsx
+++ b/data/Mörel-Filet/investment_decision/Mörel_SFH_until_2004_investment_decision.xlsx
@@ -495,7 +495,7 @@
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>74.18234948455344</v>
+        <v>19.8195072467909</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -509,19 +509,19 @@
         <v>54364.05846114377</v>
       </c>
       <c r="F2" t="n">
-        <v>74.18234948455344</v>
+        <v>20.46243272297414</v>
       </c>
       <c r="G2" t="n">
         <v>54364.05846114377</v>
       </c>
       <c r="H2" t="n">
-        <v>74.18234948455344</v>
+        <v>20.46243272297415</v>
       </c>
       <c r="I2" t="n">
         <v>54364.05846114377</v>
       </c>
       <c r="J2" t="n">
-        <v>74.18234948455344</v>
+        <v>19.8195072467909</v>
       </c>
       <c r="K2" t="n">
         <v>54364.05846114377</v>
@@ -532,7 +532,7 @@
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>343.6587530797735</v>
+        <v>103.5625399437447</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -546,19 +546,19 @@
         <v>54364.05846114377</v>
       </c>
       <c r="F3" t="n">
-        <v>365.676694128349</v>
+        <v>121.8529048434923</v>
       </c>
       <c r="G3" t="n">
         <v>54364.05846114377</v>
       </c>
       <c r="H3" t="n">
-        <v>365.676694128349</v>
+        <v>122.5590074706968</v>
       </c>
       <c r="I3" t="n">
         <v>54364.05846114377</v>
       </c>
       <c r="J3" t="n">
-        <v>343.6587530797735</v>
+        <v>103.6378782029982</v>
       </c>
       <c r="K3" t="n">
         <v>54364.05846114377</v>
@@ -569,7 +569,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>343.6587530797735</v>
+        <v>171.2085092430312</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -583,19 +583,19 @@
         <v>54364.05846114377</v>
       </c>
       <c r="F4" t="n">
-        <v>365.676694128349</v>
+        <v>173.8619242790277</v>
       </c>
       <c r="G4" t="n">
         <v>54364.05846114377</v>
       </c>
       <c r="H4" t="n">
-        <v>365.676694128349</v>
+        <v>170.5455877807926</v>
       </c>
       <c r="I4" t="n">
         <v>54364.05846114377</v>
       </c>
       <c r="J4" t="n">
-        <v>343.6587530797735</v>
+        <v>169.3530828959664</v>
       </c>
       <c r="K4" t="n">
         <v>54364.05846114377</v>
@@ -606,7 +606,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>366.5116387516129</v>
+        <v>173.8619242790276</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -620,19 +620,19 @@
         <v>54364.05846114377</v>
       </c>
       <c r="F5" t="n">
-        <v>365.676694128349</v>
+        <v>173.8619242790277</v>
       </c>
       <c r="G5" t="n">
         <v>54364.05846114377</v>
       </c>
       <c r="H5" t="n">
-        <v>365.676694128349</v>
+        <v>170.5455877807926</v>
       </c>
       <c r="I5" t="n">
         <v>54364.05846114377</v>
       </c>
       <c r="J5" t="n">
-        <v>365.4934649097531</v>
+        <v>173.1030306181045</v>
       </c>
       <c r="K5" t="n">
         <v>54364.05846114377</v>
@@ -643,7 +643,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>366.5116387516129</v>
+        <v>173.8619242790276</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>54364.05846114377</v>
       </c>
       <c r="F6" t="n">
-        <v>365.676694128349</v>
+        <v>173.8619242790277</v>
       </c>
       <c r="G6" t="n">
         <v>54364.05846114377</v>
       </c>
       <c r="H6" t="n">
-        <v>365.676694128349</v>
+        <v>170.5455877807926</v>
       </c>
       <c r="I6" t="n">
         <v>54364.05846114377</v>
       </c>
       <c r="J6" t="n">
-        <v>365.4934649097531</v>
+        <v>173.1030306181045</v>
       </c>
       <c r="K6" t="n">
         <v>54364.05846114377</v>
@@ -684,32 +684,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Mörel_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Mörel_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>81.54608769171566</v>
+        <v>59.83742831460675</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>81.54608769171566</v>
+        <v>59.83742831460675</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>46.8265402001518</v>
+        <v>34.36068880509016</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>46.8265402001518</v>
+        <v>34.36068880509016</v>
       </c>
     </row>
     <row r="8">
@@ -721,32 +721,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Mörel_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Mörel_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>81.54608769171566</v>
+        <v>59.83742831460675</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>81.54608769171566</v>
+        <v>59.83742831460675</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>60.55571878435998</v>
+        <v>44.43497639638131</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>60.55571878435998</v>
+        <v>44.43497639638131</v>
       </c>
     </row>
     <row r="9">
@@ -758,32 +758,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Mörel_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Mörel_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>81.54608769171566</v>
+        <v>59.83742831460675</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>81.54608769171566</v>
+        <v>59.83742831460675</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>66.66991032651551</v>
+        <v>48.92148836110766</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>66.66991032651551</v>
+        <v>48.92148836110766</v>
       </c>
     </row>
     <row r="10">
@@ -795,32 +795,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Mörel_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Mörel_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>81.54608769171566</v>
+        <v>59.83742831460675</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>81.54608769171566</v>
+        <v>59.83742831460675</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>70.02032774895947</v>
+        <v>51.37997984750998</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>70.02032774895947</v>
+        <v>51.37997984750998</v>
       </c>
     </row>
     <row r="11">
@@ -832,32 +832,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Mörel_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Mörel_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>81.54608769171566</v>
+        <v>59.83742831460675</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>81.54608769171566</v>
+        <v>59.83742831460675</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>72.10054529289262</v>
+        <v>52.90641565439336</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>72.10054529289262</v>
+        <v>52.90641565439336</v>
       </c>
     </row>
     <row r="12">
@@ -865,7 +865,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.009263739007058824</v>
+        <v>0.00724988270117647</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -879,19 +879,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.009263739007058824</v>
+        <v>0.007125284941876212</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.009263739007058824</v>
+        <v>0.007125284941876212</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.009263739007058824</v>
+        <v>0.00724988270117647</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -902,7 +902,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.009263739007058824</v>
+        <v>0.008458196484705884</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -916,19 +916,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.009263739007058824</v>
+        <v>0.008458196484705884</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.009263739007058824</v>
+        <v>0.008458196484705884</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.009263739007058824</v>
+        <v>0.008458196484705884</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -939,7 +939,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.01006928152941177</v>
+        <v>0.009263739007058824</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -953,19 +953,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.01006928152941177</v>
+        <v>0.009263739007058824</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.01006928152941177</v>
+        <v>0.009263739007058824</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01006928152941177</v>
+        <v>0.009263739007058824</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -976,7 +976,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.01087482405176471</v>
+        <v>0.009263739007058824</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -990,19 +990,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01087482405176471</v>
+        <v>0.009263739007058824</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.01087482405176471</v>
+        <v>0.009263739007058824</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.01087482405176471</v>
+        <v>0.009263739007058824</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1013,7 +1013,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.01087482405176471</v>
+        <v>0.009263739007058824</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1027,19 +1027,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.01087482405176471</v>
+        <v>0.009263739007058824</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.01087482405176471</v>
+        <v>0.009263739007058824</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.01087482405176471</v>
+        <v>0.009263739007058824</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1124,7 +1124,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>1.127426261646209</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1138,19 +1138,19 @@
         <v>7.189467012</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1.127426261646208</v>
       </c>
       <c r="G19" t="n">
         <v>7.189467012</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1.164290704295929</v>
       </c>
       <c r="I19" t="n">
         <v>7.189467012</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1.135862134138409</v>
       </c>
       <c r="K19" t="n">
         <v>7.189467012</v>
@@ -1161,7 +1161,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1.127426261646209</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1175,19 +1175,19 @@
         <v>7.189467012</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1.127426261646208</v>
       </c>
       <c r="G20" t="n">
         <v>7.189467012</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1.164290704295932</v>
       </c>
       <c r="I20" t="n">
         <v>7.189467012</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1.135862134138409</v>
       </c>
       <c r="K20" t="n">
         <v>7.189467012</v>
@@ -1198,7 +1198,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>1.127426261646209</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1212,19 +1212,19 @@
         <v>7.189467012</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1.127426261646208</v>
       </c>
       <c r="G21" t="n">
         <v>7.189467012</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1.164290704295929</v>
       </c>
       <c r="I21" t="n">
         <v>7.189467012</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1.135862134138409</v>
       </c>
       <c r="K21" t="n">
         <v>7.189467012</v>
@@ -2382,7 +2382,7 @@
         <v>47849</v>
       </c>
       <c r="B53" t="n">
-        <v>9.58903928348472</v>
+        <v>7.801301246595325</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2396,19 +2396,19 @@
         <v>84.56854600612546</v>
       </c>
       <c r="F53" t="n">
-        <v>9.103349407413202</v>
+        <v>6.882881010350001</v>
       </c>
       <c r="G53" t="n">
         <v>84.56854600612546</v>
       </c>
       <c r="H53" t="n">
-        <v>9.103349407413202</v>
+        <v>6.822449317571388</v>
       </c>
       <c r="I53" t="n">
         <v>33.61451895669639</v>
       </c>
       <c r="J53" t="n">
-        <v>9.589039283484722</v>
+        <v>7.796961359870857</v>
       </c>
       <c r="K53" t="n">
         <v>33.61451895669639</v>
@@ -2419,7 +2419,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>27.50565739810569</v>
+        <v>27.66108954252064</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2433,19 +2433,19 @@
         <v>84.56854600612546</v>
       </c>
       <c r="F54" t="n">
-        <v>26.31552182910831</v>
+        <v>25.79104855608815</v>
       </c>
       <c r="G54" t="n">
         <v>84.56854600612546</v>
       </c>
       <c r="H54" t="n">
-        <v>26.31552182910831</v>
+        <v>25.82005052459941</v>
       </c>
       <c r="I54" t="n">
         <v>39.82335072019411</v>
       </c>
       <c r="J54" t="n">
-        <v>27.50565739810569</v>
+        <v>27.67731558487829</v>
       </c>
       <c r="K54" t="n">
         <v>39.82335072019411</v>
@@ -2456,7 +2456,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>28.12909420918999</v>
+        <v>27.79104855608815</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2470,19 +2470,19 @@
         <v>84.56854600612546</v>
       </c>
       <c r="F55" t="n">
-        <v>27.56644091097885</v>
+        <v>27.34101391989036</v>
       </c>
       <c r="G55" t="n">
         <v>84.56854600612546</v>
       </c>
       <c r="H55" t="n">
-        <v>27.56644091097885</v>
+        <v>27.41949781875952</v>
       </c>
       <c r="I55" t="n">
         <v>43.81815082035252</v>
       </c>
       <c r="J55" t="n">
-        <v>28.12909420918999</v>
+        <v>27.79768521978896</v>
       </c>
       <c r="K55" t="n">
         <v>43.81815082035252</v>
@@ -2493,7 +2493,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>27.96922690107963</v>
+        <v>27.34101391989036</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2507,19 +2507,19 @@
         <v>84.56854600612546</v>
       </c>
       <c r="F56" t="n">
-        <v>26.64225576332853</v>
+        <v>26.63842306967327</v>
       </c>
       <c r="G56" t="n">
         <v>84.56854600612546</v>
       </c>
       <c r="H56" t="n">
-        <v>26.64225576332853</v>
+        <v>26.62613311676805</v>
       </c>
       <c r="I56" t="n">
         <v>46.59509199595038</v>
       </c>
       <c r="J56" t="n">
-        <v>27.94676718397978</v>
+        <v>27.31251864045818</v>
       </c>
       <c r="K56" t="n">
         <v>46.59509199595038</v>
@@ -2789,7 +2789,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>8.083381885379028</v>
+        <v>3.477181081814021</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2803,19 +2803,19 @@
         <v>84.56854600612546</v>
       </c>
       <c r="F64" t="n">
-        <v>8.787827578304897</v>
+        <v>5.324017469026196</v>
       </c>
       <c r="G64" t="n">
         <v>84.56854600612546</v>
       </c>
       <c r="H64" t="n">
-        <v>8.787827578304897</v>
+        <v>5.324017469026193</v>
       </c>
       <c r="I64" t="n">
         <v>84.56854600612546</v>
       </c>
       <c r="J64" t="n">
-        <v>8.083381885379028</v>
+        <v>3.477181081814019</v>
       </c>
       <c r="K64" t="n">
         <v>84.56854600612546</v>
@@ -2826,7 +2826,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>9.955837302121809</v>
+        <v>6.324017469026208</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2840,19 +2840,19 @@
         <v>84.56854600612546</v>
       </c>
       <c r="F65" t="n">
-        <v>10.53690849643435</v>
+        <v>6.774052105223994</v>
       </c>
       <c r="G65" t="n">
         <v>84.56854600612546</v>
       </c>
       <c r="H65" t="n">
-        <v>10.53690849643435</v>
+        <v>6.724570174866088</v>
       </c>
       <c r="I65" t="n">
         <v>84.56854600612546</v>
       </c>
       <c r="J65" t="n">
-        <v>9.978297019221657</v>
+        <v>6.324017469026195</v>
       </c>
       <c r="K65" t="n">
         <v>84.56854600612546</v>
@@ -2863,7 +2863,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>15.27424973064236</v>
+        <v>9.792846715595525</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2877,19 +2877,19 @@
         <v>84.56854600612546</v>
       </c>
       <c r="F66" t="n">
-        <v>16.61963876449487</v>
+        <v>10.49543756581263</v>
       </c>
       <c r="G66" t="n">
         <v>84.56854600612546</v>
       </c>
       <c r="H66" t="n">
-        <v>16.61963876449487</v>
+        <v>10.53888244309691</v>
       </c>
       <c r="I66" t="n">
         <v>84.56854600612546</v>
       </c>
       <c r="J66" t="n">
-        <v>15.31916916484206</v>
+        <v>9.828471330253612</v>
       </c>
       <c r="K66" t="n">
         <v>84.56854600612546</v>
@@ -3108,13 +3108,13 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>2.567101656914399</v>
+        <v>84.56854600612546</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>2.567101656914399</v>
+        <v>84.56854600612546</v>
       </c>
     </row>
     <row r="73">
@@ -3145,13 +3145,13 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>4.347693440261766</v>
+        <v>84.56854600612546</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>4.347693440261766</v>
+        <v>84.56854600612546</v>
       </c>
     </row>
     <row r="74">
@@ -3182,13 +3182,13 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>5.723652447911148</v>
+        <v>84.56854600612546</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>5.723652447911148</v>
+        <v>84.56854600612546</v>
       </c>
     </row>
     <row r="75">
@@ -3219,13 +3219,13 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>6.842309212961666</v>
+        <v>84.56854600612546</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>6.842309212961666</v>
+        <v>84.56854600612546</v>
       </c>
     </row>
     <row r="76">
@@ -3256,13 +3256,13 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>7.781271170905232</v>
+        <v>84.56854600612546</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>7.781271170905232</v>
+        <v>84.56854600612546</v>
       </c>
     </row>
     <row r="77">
@@ -3293,13 +3293,13 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>2.567101656914399</v>
+        <v>84.56854600612546</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>2.567101656914399</v>
+        <v>84.56854600612546</v>
       </c>
     </row>
     <row r="78">
@@ -3330,13 +3330,13 @@
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>4.347693440261766</v>
+        <v>84.56854600612546</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>4.347693440261766</v>
+        <v>84.56854600612546</v>
       </c>
     </row>
     <row r="79">
@@ -3367,13 +3367,13 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>5.723652447911148</v>
+        <v>84.56854600612546</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>5.723652447911148</v>
+        <v>84.56854600612546</v>
       </c>
     </row>
     <row r="80">
@@ -3404,13 +3404,13 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>6.842309212961666</v>
+        <v>84.56854600612546</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>6.842309212961666</v>
+        <v>84.56854600612546</v>
       </c>
     </row>
     <row r="81">
@@ -3441,13 +3441,13 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>7.781271170905232</v>
+        <v>84.56854600612546</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>7.781271170905232</v>
+        <v>84.56854600612546</v>
       </c>
     </row>
     <row r="82">
